--- a/runs/RELX/2026-10-14/bear/scratch/g_beta_blume/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_beta_blume/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2193.76387581693</v>
+        <v>2231.379554461737</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.08366999999999999</v>
+        <v>0.0790028</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.07903090944000001</v>
+        <v>0.074961951136</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11565.06072544334</v>
+        <v>11672.77586242135</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>48775.65925357705</v>
+        <v>52386.63229312262</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>34637.82896632633</v>
+        <v>37840.03805618015</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46202.88969176968</v>
+        <v>49512.8139186015</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>39205.88969176968</v>
+        <v>42515.8139186015</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>38480.52693777143</v>
+        <v>41852.67788747881</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>22.06762587762231</v>
+        <v>24.00147064230944</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2206.762587762231</v>
+        <v>2400.147064230944</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.2036223068</v>
+        <v>-0.1338336109</v>
       </c>
     </row>
   </sheetData>
